--- a/jogos_2026-11-05.xlsx
+++ b/jogos_2026-11-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2218,156 +2218,319 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>-1</v>
+      </c>
+      <c r="AN12">
+        <v>-1</v>
+      </c>
+      <c r="AO12">
+        <v>-1</v>
+      </c>
+      <c r="AP12">
+        <v>-1</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2026-11-05 19:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Bahia</t>
         </is>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N12">
+      <c r="N13">
         <v>1.88</v>
       </c>
-      <c r="O12">
+      <c r="O13">
         <v>3.92</v>
       </c>
-      <c r="P12">
+      <c r="P13">
         <v>3.92</v>
       </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
-      </c>
-      <c r="X12">
-        <v>0</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
-      </c>
-      <c r="Z12">
-        <v>0</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0</v>
-      </c>
-      <c r="AC12">
-        <v>0</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AI13" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ12">
-        <v>0</v>
-      </c>
-      <c r="AK12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>-1</v>
-      </c>
-      <c r="AN12">
-        <v>-1</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>-1</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>2026-11-05 21:30:00</t>
         </is>

--- a/jogos_2026-11-05.xlsx
+++ b/jogos_2026-11-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU13"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2381,156 +2381,319 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>-1</v>
+      </c>
+      <c r="AN13">
+        <v>-1</v>
+      </c>
+      <c r="AO13">
+        <v>-1</v>
+      </c>
+      <c r="AP13">
+        <v>-1</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2026-11-05 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Bahia</t>
         </is>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="inlineStr">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N13">
+      <c r="N14">
         <v>1.88</v>
       </c>
-      <c r="O13">
+      <c r="O14">
         <v>3.92</v>
       </c>
-      <c r="P13">
+      <c r="P14">
         <v>3.92</v>
       </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI13" t="inlineStr">
+      <c r="AI14" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-1</v>
-      </c>
-      <c r="AN13">
-        <v>-1</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>-1</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>2026-11-05 21:30:00</t>
         </is>

--- a/jogos_2026-11-05.xlsx
+++ b/jogos_2026-11-05.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU14"/>
+  <dimension ref="A1:AU15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,27 +1240,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00:00</t>
+          <t>2026-11-05 10:30:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-11-05 12:10:00</t>
+          <t>2026-11-05 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Abha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-11-05 12:20:00</t>
+          <t>2026-11-05 12:10:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-11-05 14:30:00</t>
+          <t>2026-11-05 12:20:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-11-05 16:45:00</t>
+          <t>2026-11-05 14:30:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>7.13</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-11-05 19:30:00</t>
+          <t>2026-11-05 16:45:00</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>7.13</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Univ. Concepción</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-11-05 20:00:00</t>
+          <t>2026-11-05 19:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,156 +2544,319 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Univ. Concepción</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>-1</v>
+      </c>
+      <c r="AN14">
+        <v>-1</v>
+      </c>
+      <c r="AO14">
+        <v>-1</v>
+      </c>
+      <c r="AP14">
+        <v>-1</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2026-11-05 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Brazil Serie A</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Cruzeiro</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Bahia</t>
         </is>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14" t="inlineStr">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N14">
+      <c r="N15">
         <v>1.88</v>
       </c>
-      <c r="O14">
+      <c r="O15">
         <v>3.92</v>
       </c>
-      <c r="P14">
+      <c r="P15">
         <v>3.92</v>
       </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>0</v>
-      </c>
-      <c r="V14">
-        <v>0</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>0</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>0</v>
-      </c>
-      <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>0</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>0</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
+      <c r="AI15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ14">
-        <v>0</v>
-      </c>
-      <c r="AK14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>-1</v>
-      </c>
-      <c r="AN14">
-        <v>-1</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>-1</v>
-      </c>
-      <c r="AQ14">
-        <v>0</v>
-      </c>
-      <c r="AR14">
-        <v>0</v>
-      </c>
-      <c r="AS14">
-        <v>0</v>
-      </c>
-      <c r="AT14">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
+      <c r="AJ15">
+        <v>0</v>
+      </c>
+      <c r="AK15">
+        <v>0</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>-1</v>
+      </c>
+      <c r="AN15">
+        <v>-1</v>
+      </c>
+      <c r="AO15">
+        <v>-1</v>
+      </c>
+      <c r="AP15">
+        <v>-1</v>
+      </c>
+      <c r="AQ15">
+        <v>0</v>
+      </c>
+      <c r="AR15">
+        <v>0</v>
+      </c>
+      <c r="AS15">
+        <v>0</v>
+      </c>
+      <c r="AT15">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>2026-11-05 21:30:00</t>
         </is>

--- a/jogos_2026-11-05.xlsx
+++ b/jogos_2026-11-05.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL5">
         <v>0</v>
